--- a/tlumaczenia_LT_LV.xlsx
+++ b/tlumaczenia_LT_LV.xlsx
@@ -1461,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1744,6 +1744,204 @@
       </c>
       <c r="D15" s="2" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>24V, góra/dół, 100kHz</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>24V, aukštyn/žemyn, 100kHz</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>24V, uz augšu/leju, 100kHz</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>24V, góra, bramkowany</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>24V, aukštyn, su blokavimu</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24V, uz augšu, ar bloķēšanu</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>góra/dół, z wyjściem cyfrowym</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>aukštyn/žemyn, su skaitmeniniu išėjimu</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>uz augšu/leju, ar digitālo izeju</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2x góra, 16bit</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2x aukštyn, 16bit</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2x uz augšu, 16bit</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>24V, 2x góra/dół, 16bit, 500Hz</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>24V, 2x aukštyn/žemyn, 16bit, 500Hz</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>24V, 2x uz augšu/leju, 16bit, 500Hz</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2 wyjścia z regul. szerokości impulsu (PWM)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2 išėjimai su impulso pločio reguliavimu (PWM)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2 izejas ar impulsa platuma regulēšanu (PWM)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>podłączanie 2-, 3-, 4-przewodowe</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2, 3, 4 laidų prijungimas</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2, 3, 4 vadu pieslēgums</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>4FDI/2FDO; PROFIsafe; logika</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>4FDI/2FDO; PROFIsafe; logika</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>4FDI/2FDO; PROFIsafe; loģika</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>4FDI/4FDO; PROFIsafe; logika</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>4FDI/4FDO; PROFIsafe; logika</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4FDI/4FDO; PROFIsafe; loģika</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>4 AI do RTD, 2-, 3-, 4-przewodowe</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>4 AI RTD, 2, 3, 4 laidų</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4 AI RTD, 2, 3, 4 vadu</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>4 AO konfigurowalne napięciowe/prądowe (U/I)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>4 AO konfigūruojami įtampos/srovės (U/I)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4 AO konfigurējamas sprieguma/strāvas (U/I)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
